--- a/testdatafolder/UI_Validation_Results.xlsx
+++ b/testdatafolder/UI_Validation_Results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="25">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -29,25 +29,49 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Loan Tenure Calculator</t>
+  </si>
+  <si>
+    <t>Loan Amount</t>
+  </si>
+  <si>
+    <t>1500000</t>
+  </si>
+  <si>
+    <t>15,00,000</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Monthly EMI</t>
+  </si>
+  <si>
+    <t>131525</t>
+  </si>
+  <si>
+    <t>1,31,525.27</t>
+  </si>
+  <si>
+    <t>Interest Rate</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>EMI Calculator</t>
+  </si>
+  <si>
     <t>Loan Amount Calculator</t>
   </si>
   <si>
-    <t>Monthly EMI</t>
-  </si>
-  <si>
-    <t>131525</t>
-  </si>
-  <si>
     <t>1,31,525.00</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>Interest Rate</t>
-  </si>
-  <si>
-    <t>9.5</t>
+    <t>Loan Tenure</t>
+  </si>
+  <si>
+    <t>1.0 Years</t>
   </si>
   <si>
     <t>Loan Term</t>
@@ -62,31 +86,7 @@
     <t>Total Loan Amount</t>
   </si>
   <si>
-    <t>1500000</t>
-  </si>
-  <si>
     <t>14,99,997</t>
-  </si>
-  <si>
-    <t>EMI Calculator</t>
-  </si>
-  <si>
-    <t>Loan Amount</t>
-  </si>
-  <si>
-    <t>15,00,000</t>
-  </si>
-  <si>
-    <t>1,31,525.27</t>
-  </si>
-  <si>
-    <t>Loan Tenure Calculator</t>
-  </si>
-  <si>
-    <t>Loan Tenure</t>
-  </si>
-  <si>
-    <t>1.0 Years</t>
   </si>
 </sst>
 </file>
@@ -181,7 +181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="20.2734375" customWidth="true" bestFit="true"/>
@@ -236,7 +236,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s" s="2">
         <v>9</v>
@@ -247,13 +247,13 @@
         <v>5</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s" s="2">
         <v>9</v>
@@ -261,16 +261,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s" s="2">
         <v>9</v>
@@ -278,13 +278,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>17</v>
@@ -295,16 +295,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s" s="2">
         <v>9</v>
@@ -312,16 +312,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>10</v>
-      </c>
       <c r="C8" t="s" s="0">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s" s="2">
         <v>9</v>
@@ -329,16 +329,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s" s="2">
         <v>9</v>
@@ -346,16 +346,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s" s="2">
         <v>9</v>
@@ -363,16 +363,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s" s="2">
         <v>9</v>
@@ -380,16 +380,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s" s="2">
         <v>9</v>
@@ -397,16 +397,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B13" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>7</v>
-      </c>
       <c r="D13" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s" s="2">
         <v>9</v>
@@ -414,7 +414,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>10</v>
@@ -423,7 +423,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s" s="2">
         <v>9</v>
@@ -431,256 +431,18 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>23</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>24</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="D16" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="D21" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D22" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="D23" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C24" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="D24" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="C25" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="D25" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C26" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="D26" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C27" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D27" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C28" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="D28" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="C29" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="D29" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="E29" t="s" s="2">
         <v>9</v>
       </c>
     </row>
